--- a/chapter7_config.xlsx
+++ b/chapter7_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JonathanVandenBerk\Desktop\Cursor_GIT\Magics_cursor_AI_workspace\Projects\VISION_test_plan_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED96583-1573-4C78-9DFC-6DC2B944C9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050C169D-8850-4E08-B90C-588726F6B284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25770" yWindow="720" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1850,9 +1850,6 @@
     <t>Fixed to 10b for all tests</t>
   </si>
   <si>
-    <t>Features are included as functional test: Exposure time, sub-sampling, X-Y mirroring, ADC resolution</t>
-  </si>
-  <si>
     <t>M3802</t>
   </si>
   <si>
@@ -1869,6 +1866,9 @@
   </si>
   <si>
     <t>Only tested at speed during characterization (FHD30 mode), production testing uses FHD10, HD40 and VGA50 mode what is at half of the max speed</t>
+  </si>
+  <si>
+    <t>Features are tested during characterization: Exposure time, sub-sampling, X-Y mirroring, ADC resolution</t>
   </si>
 </sst>
 </file>
@@ -4640,15 +4640,15 @@
         <v>35</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -4673,15 +4673,15 @@
         <v>35</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
       <c r="M29" s="9" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -4977,10 +4977,10 @@
         <v>595</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J41" s="24" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K41" s="23"/>
       <c r="L41" s="23"/>
@@ -5006,10 +5006,10 @@
         <v>594</v>
       </c>
       <c r="I42" s="24" t="s">
+        <v>607</v>
+      </c>
+      <c r="J42" s="24" t="s">
         <v>608</v>
-      </c>
-      <c r="J42" s="24" t="s">
-        <v>609</v>
       </c>
       <c r="K42" s="23"/>
       <c r="L42" s="23"/>
@@ -5038,7 +5038,7 @@
         <v>596</v>
       </c>
       <c r="J43" s="24" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K43" s="23"/>
       <c r="L43" s="23"/>
@@ -5067,7 +5067,7 @@
         <v>597</v>
       </c>
       <c r="J44" s="24" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K44" s="23"/>
       <c r="L44" s="23"/>
@@ -5096,7 +5096,7 @@
         <v>598</v>
       </c>
       <c r="J45" s="24" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K45" s="23"/>
       <c r="L45" s="23"/>
@@ -5125,7 +5125,7 @@
         <v>600</v>
       </c>
       <c r="J46" s="24" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K46" s="23"/>
       <c r="L46" s="23"/>
@@ -5154,7 +5154,7 @@
         <v>601</v>
       </c>
       <c r="J47" s="24" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K47" s="23"/>
       <c r="L47" s="23"/>
@@ -5183,7 +5183,7 @@
         <v>602</v>
       </c>
       <c r="J48" s="24" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K48" s="23"/>
       <c r="L48" s="23"/>
@@ -5214,7 +5214,7 @@
         <v>603</v>
       </c>
       <c r="J49" s="24" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K49" s="23"/>
       <c r="L49" s="23"/>
@@ -5267,7 +5267,7 @@
       <c r="K51" s="23"/>
       <c r="L51" s="23"/>
       <c r="M51" s="24" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">

--- a/chapter7_config.xlsx
+++ b/chapter7_config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JonathanVandenBerk\Desktop\Cursor_GIT\Magics_cursor_AI_workspace\Projects\VISION_test_plan_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050C169D-8850-4E08-B90C-588726F6B284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B015E48C-F0A4-49D2-8E96-D26876C163FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="614">
   <si>
     <t>Include</t>
   </si>
@@ -380,6 +380,15 @@
     <t>100</t>
   </si>
   <si>
+    <t>M0130</t>
+  </si>
+  <si>
+    <t>T0024</t>
+  </si>
+  <si>
+    <t>Only tested at speed during characterization (FHD30 mode), production testing uses FHD10, HD40 and VGA50 mode what is at half of the max speed</t>
+  </si>
+  <si>
     <t>Data output line speed</t>
   </si>
   <si>
@@ -446,6 +455,9 @@
     <t>1920 (H) x 1080 (V)</t>
   </si>
   <si>
+    <t>Guaranteed by design</t>
+  </si>
+  <si>
     <t>Pixel size</t>
   </si>
   <si>
@@ -464,31 +476,46 @@
     <t>Rolling shutter</t>
   </si>
   <si>
-    <t>Full well charge</t>
-  </si>
-  <si>
-    <t>94000</t>
+    <t>Saturation limit</t>
   </si>
   <si>
     <t>e-</t>
   </si>
   <si>
+    <t>M3805</t>
+  </si>
+  <si>
+    <t>T0038</t>
+  </si>
+  <si>
+    <t>Typical pre-irrad value. Related to design target full-well charge. Tested only during characterization</t>
+  </si>
+  <si>
     <t>Conversion gain</t>
   </si>
   <si>
-    <t>0.01</t>
-  </si>
-  <si>
-    <t>Responsivity</t>
-  </si>
-  <si>
-    <t>0.009</t>
-  </si>
-  <si>
-    <t>Temporal noise</t>
-  </si>
-  <si>
-    <t>66</t>
+    <t>mV/e-</t>
+  </si>
+  <si>
+    <t>M3802</t>
+  </si>
+  <si>
+    <t>System gain (K)</t>
+  </si>
+  <si>
+    <t>DN_10bit/e-</t>
+  </si>
+  <si>
+    <t>M3804</t>
+  </si>
+  <si>
+    <t>10-bit equivalent. K = conversion gain / ADC gain</t>
+  </si>
+  <si>
+    <t>Read noise</t>
+  </si>
+  <si>
+    <t>M3812</t>
   </si>
   <si>
     <t>Dynamic range</t>
@@ -500,633 +527,669 @@
     <t>dB</t>
   </si>
   <si>
+    <t>M3807</t>
+  </si>
+  <si>
     <t>SNR_MAX</t>
   </si>
   <si>
-    <t>49.5</t>
+    <t>M3806</t>
   </si>
   <si>
     <t>Dark current (DC)</t>
   </si>
   <si>
+    <t>e-/s/px</t>
+  </si>
+  <si>
+    <t>M3813</t>
+  </si>
+  <si>
+    <t>Dark current non uniformity (DCNU)</t>
+  </si>
+  <si>
+    <t>M3815</t>
+  </si>
+  <si>
+    <t>Dark signal non uniformity (DSNU)</t>
+  </si>
+  <si>
+    <t>M3808</t>
+  </si>
+  <si>
+    <t>Measured after Column FPN (CFPN) correction</t>
+  </si>
+  <si>
+    <t>Photo response non uniformity (PRNU)</t>
+  </si>
+  <si>
+    <t>% of mean</t>
+  </si>
+  <si>
+    <t>M3809</t>
+  </si>
+  <si>
+    <t>Measured after Column FPN (CFPN) correction at 50% dynamic range</t>
+  </si>
+  <si>
+    <t>Column Fixed-Pattern Noise (CFPN)</t>
+  </si>
+  <si>
+    <t>DN_10bit</t>
+  </si>
+  <si>
+    <t>M3818</t>
+  </si>
+  <si>
+    <t>10-bit equivalent.</t>
+  </si>
+  <si>
+    <t>Color filters</t>
+  </si>
+  <si>
+    <t>BayerRG (Bayer RGGB)</t>
+  </si>
+  <si>
+    <t>Programmable features</t>
+  </si>
+  <si>
+    <t>Sensor parameters</t>
+  </si>
+  <si>
+    <t>Features are tested during characterization: Exposure time, sub-sampling, X-Y mirroring, ADC resolution</t>
+  </si>
+  <si>
+    <t>ADC resolution</t>
+  </si>
+  <si>
+    <t>10 and 12 bit</t>
+  </si>
+  <si>
+    <t>Interface</t>
+  </si>
+  <si>
+    <t>10/12b parallel output</t>
+  </si>
+  <si>
+    <t>Fixed to 10b for all tests</t>
+  </si>
+  <si>
+    <t>Cover glass lid</t>
+  </si>
+  <si>
+    <t>Corning 7980 0F</t>
+  </si>
+  <si>
+    <t>Chapter 7 Configuration File — README</t>
+  </si>
+  <si>
+    <t>This workbook controls which parameters appear in Chapter 7 of the</t>
+  </si>
+  <si>
+    <t>Vision Series Test Plan.  One sheet per product.</t>
+  </si>
+  <si>
+    <t>COLUMN DESCRIPTIONS (IC sheets: CXP00002, IMG002X1, PSU00001):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Include        → TRUE to include this row in the report, FALSE to exclude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Section        → Category group (renders as bold header in the report table)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Parameter      → Human-readable parameter name shown in the report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Datasheet_Label→ Label as it appears in the product datasheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  DS_Min/Typ/Max → Values from the product datasheet (BLUE header)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Unit           → Measurement unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Mxxxx          → Measurement ID in the check_limits database (editable!)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Test_Proc      → Test procedure reference (Txxxx or Functional/VER/etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  LSL            → Lower Specification Limit from check_limits (ORANGE header)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  USL            → Upper Specification Limit from check_limits (ORANGE header)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Comment        → Free-text note shown in the report Comment column</t>
+  </si>
+  <si>
+    <t>VIS100xx sheet has no Mxxxx/LSL/USL columns (module-level functional test).</t>
+  </si>
+  <si>
+    <t>HOW TO UPDATE:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1. Set Include=FALSE for any parameter you want to hide from the report.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2. Change the Mxxxx column to fix an incorrect measurement ID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3. Edit LSL/USL if the auto-populated values need correction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4. Add a Comment to explain why a parameter has no Mxxxx, is covered by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     another measurement, or any other note you want in the report.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  5. You can add new rows — just fill in all columns and set Include=TRUE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  6. You can reorder rows by cut-pasting — the section grouping is driven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     by the Section column, not by row position.</t>
+  </si>
+  <si>
+    <t>WHEN DONE EDITING:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Save this file, then run:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    python chapter7_config_manager.py report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  This will update Vision_Series_Test_Plan.md Chapter 7 and regenerate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  the Word document.</t>
+  </si>
+  <si>
+    <t>COLOR LEGEND:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Blue header columns  (DS_Min/Typ/Max) → values from the DATASHEET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Orange header columns (LSL/USL)        → values from CHECK_LIMITS tester DB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Grey rows                              → section headers (category grouping)</t>
+  </si>
+  <si>
+    <t>VDD3V3 supply voltage</t>
+  </si>
+  <si>
+    <t>VDD3V3</t>
+  </si>
+  <si>
+    <t>Operation temperature (junction)</t>
+  </si>
+  <si>
+    <t>-40</t>
+  </si>
+  <si>
+    <t>3.3V total supply current (average)</t>
+  </si>
+  <si>
+    <t>IVDD3V3_TOTAL_AVG</t>
+  </si>
+  <si>
+    <t>82.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum of analog + digital </t>
+  </si>
+  <si>
+    <t>3.3V digital supply current (average)</t>
+  </si>
+  <si>
+    <t>IVDD3V3_DIG_AVG</t>
+  </si>
+  <si>
+    <t>14.45</t>
+  </si>
+  <si>
+    <t>18.6</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>M0041</t>
+  </si>
+  <si>
+    <t>Channel combines DIG+PLL</t>
+  </si>
+  <si>
+    <t>3.3V analog supply current (average)</t>
+  </si>
+  <si>
+    <t>IVDD3V3_ANA_AVG</t>
+  </si>
+  <si>
+    <t>49.8</t>
+  </si>
+  <si>
+    <t>M0035</t>
+  </si>
+  <si>
+    <t>Active mode measurement</t>
+  </si>
+  <si>
+    <t>3.3V PLL supply current (average)</t>
+  </si>
+  <si>
+    <t>IVDD3V3_PLL_AVG</t>
+  </si>
+  <si>
+    <t>13.93</t>
+  </si>
+  <si>
+    <t>Included in DIG, no separate Power supply channel</t>
+  </si>
+  <si>
+    <t>Power consumption</t>
+  </si>
+  <si>
+    <t>Total power consumption</t>
+  </si>
+  <si>
+    <t>271.55</t>
+  </si>
+  <si>
+    <t>mW</t>
+  </si>
+  <si>
+    <t>Derived from IDD x VDD</t>
+  </si>
+  <si>
+    <t>Logic level inputs (GPIO)</t>
+  </si>
+  <si>
+    <t>VIL (GPIO input low threshold)</t>
+  </si>
+  <si>
+    <t>VIL</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>470</t>
+  </si>
+  <si>
+    <t>635</t>
+  </si>
+  <si>
+    <t>mV</t>
+  </si>
+  <si>
+    <t>VIH (GPIO input high threshold)</t>
+  </si>
+  <si>
+    <t>VIH</t>
+  </si>
+  <si>
+    <t>443</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>715</t>
+  </si>
+  <si>
+    <t>Hysteresis (GPIO)</t>
+  </si>
+  <si>
+    <t>Hysteresis</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>Logic level inputs (Video pins)</t>
+  </si>
+  <si>
+    <t>VIL (Video input low threshold)</t>
+  </si>
+  <si>
+    <t>1.147</t>
+  </si>
+  <si>
+    <t>1.328</t>
+  </si>
+  <si>
+    <t>1.689</t>
+  </si>
+  <si>
+    <t>VIH (Video input high threshold)</t>
+  </si>
+  <si>
+    <t>1.482</t>
+  </si>
+  <si>
+    <t>1.714</t>
+  </si>
+  <si>
+    <t>2.282</t>
+  </si>
+  <si>
+    <t>Hysteresis (Video)</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>387</t>
+  </si>
+  <si>
+    <t>593</t>
+  </si>
+  <si>
+    <t>M0021</t>
+  </si>
+  <si>
+    <t>Digital output levels (GPIO)</t>
+  </si>
+  <si>
+    <t>VOL (GPIO output low voltage)</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>M0029</t>
+  </si>
+  <si>
+    <t>VOH (GPIO output high voltage)</t>
+  </si>
+  <si>
+    <t>VDD-0.3</t>
+  </si>
+  <si>
+    <t>M0030</t>
+  </si>
+  <si>
+    <t>IOL (GPIO output low current)</t>
+  </si>
+  <si>
+    <t>IOL</t>
+  </si>
+  <si>
+    <t>M0031</t>
+  </si>
+  <si>
+    <t>T0006</t>
+  </si>
+  <si>
+    <t>IOH (GPIO output high current)</t>
+  </si>
+  <si>
+    <t>IOH</t>
+  </si>
+  <si>
+    <t>-20</t>
+  </si>
+  <si>
+    <t>M0032</t>
+  </si>
+  <si>
+    <t>Data rates</t>
+  </si>
+  <si>
+    <t>Parallel video data rate</t>
+  </si>
+  <si>
+    <t>DRin,par</t>
+  </si>
+  <si>
+    <t>M0156</t>
+  </si>
+  <si>
+    <t>T0023</t>
+  </si>
+  <si>
+    <t>Functional test</t>
+  </si>
+  <si>
+    <t>Downlink data rate (CXP)</t>
+  </si>
+  <si>
+    <t>DRdown</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>Gbps</t>
+  </si>
+  <si>
+    <t>T0022/T0023</t>
+  </si>
+  <si>
+    <t>Uplink data rate (CXP)</t>
+  </si>
+  <si>
+    <t>DRup</t>
+  </si>
+  <si>
+    <t>20.833</t>
+  </si>
+  <si>
+    <t>Mbps</t>
+  </si>
+  <si>
+    <t>T0020/T0021</t>
+  </si>
+  <si>
+    <t>Transceiver load impedance</t>
+  </si>
+  <si>
+    <t>ZL</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>Ω</t>
+  </si>
+  <si>
+    <t>Crystal oscillator</t>
+  </si>
+  <si>
+    <t>Crystal frequency</t>
+  </si>
+  <si>
+    <t>fXTAL</t>
+  </si>
+  <si>
+    <t>M0131</t>
+  </si>
+  <si>
+    <t>T0013</t>
+  </si>
+  <si>
+    <t>CAM LDO outputs</t>
+  </si>
+  <si>
+    <t>VDD1V8_CAM supply voltage</t>
+  </si>
+  <si>
+    <t>V_VDD1V8_CAM</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>1.9</t>
+  </si>
+  <si>
+    <t>M0214</t>
+  </si>
+  <si>
+    <t>T0012</t>
+  </si>
+  <si>
+    <t>VDD1V8_CAM load current</t>
+  </si>
+  <si>
+    <t>I_VDD1V8_CAM</t>
+  </si>
+  <si>
+    <t>VDD1V2_CAM reference voltage</t>
+  </si>
+  <si>
+    <t>V_VDD1V2_CAM</t>
+  </si>
+  <si>
+    <t>M0109</t>
+  </si>
+  <si>
+    <t>T0011</t>
+  </si>
+  <si>
+    <t>&gt; 1 MGy (100 Mrad)</t>
+  </si>
+  <si>
+    <t>&gt; 60</t>
+  </si>
+  <si>
+    <t>Input voltage (PVin, Vin)</t>
+  </si>
+  <si>
+    <t>PVin, Vin</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Output voltage (Vout)</t>
+  </si>
+  <si>
+    <t>Vout</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>Output current (active cooling)</t>
+  </si>
+  <si>
+    <t>Iout</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Switching frequency</t>
+  </si>
+  <si>
+    <t>fsw</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Input current (control, disabled)</t>
+  </si>
+  <si>
+    <t>Iin</t>
+  </si>
+  <si>
+    <t>Power short input</t>
+  </si>
+  <si>
+    <t>-10</t>
+  </si>
+  <si>
+    <t>M0001</t>
+  </si>
+  <si>
+    <t>T0001</t>
+  </si>
+  <si>
+    <t>Power short output</t>
+  </si>
+  <si>
+    <t>M0002</t>
+  </si>
+  <si>
+    <t>T0002</t>
+  </si>
+  <si>
+    <t>Enable</t>
+  </si>
+  <si>
+    <t>Enable start threshold (VIH)</t>
+  </si>
+  <si>
+    <t>EnStartTh</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>0.815</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>M0007</t>
+  </si>
+  <si>
+    <t>Enable stop threshold (VIL)</t>
+  </si>
+  <si>
+    <t>EnStopTh</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>M0008</t>
+  </si>
+  <si>
+    <t>Enable hysteresis</t>
+  </si>
+  <si>
+    <t>Hyst</t>
+  </si>
+  <si>
     <t>0.05</t>
   </si>
   <si>
-    <t>Dark current non uniformity (DCNU)</t>
-  </si>
-  <si>
-    <t>42.8</t>
-  </si>
-  <si>
-    <t>Dark signal non uniformity (DSNU)</t>
-  </si>
-  <si>
-    <t>587.2</t>
-  </si>
-  <si>
-    <t>Photo response non uniformity (PRNU)</t>
-  </si>
-  <si>
-    <t>&lt; tba</t>
-  </si>
-  <si>
-    <t>Color filters</t>
-  </si>
-  <si>
-    <t>BayerRG (Bayer RGGB)</t>
-  </si>
-  <si>
-    <t>Programmable features</t>
-  </si>
-  <si>
-    <t>Sensor parameters</t>
-  </si>
-  <si>
-    <t>ADC resolution</t>
-  </si>
-  <si>
-    <t>10 and 12 bit</t>
-  </si>
-  <si>
-    <t>Interface</t>
-  </si>
-  <si>
-    <t>10/12b parallel output</t>
-  </si>
-  <si>
-    <t>Cover glass lid</t>
-  </si>
-  <si>
-    <t>Corning 7980 0F</t>
-  </si>
-  <si>
-    <t>Chapter 7 Configuration File — README</t>
-  </si>
-  <si>
-    <t>This workbook controls which parameters appear in Chapter 7 of the</t>
-  </si>
-  <si>
-    <t>Vision Series Test Plan.  One sheet per product.</t>
-  </si>
-  <si>
-    <t>COLUMN DESCRIPTIONS (IC sheets: CXP00002, IMG002X1, PSU00001):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Include        → TRUE to include this row in the report, FALSE to exclude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Section        → Category group (renders as bold header in the report table)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Parameter      → Human-readable parameter name shown in the report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Datasheet_Label→ Label as it appears in the product datasheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  DS_Min/Typ/Max → Values from the product datasheet (BLUE header)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Unit           → Measurement unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Mxxxx          → Measurement ID in the check_limits database (editable!)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Test_Proc      → Test procedure reference (Txxxx or Functional/VER/etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  LSL            → Lower Specification Limit from check_limits (ORANGE header)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  USL            → Upper Specification Limit from check_limits (ORANGE header)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Comment        → Free-text note shown in the report Comment column</t>
-  </si>
-  <si>
-    <t>VIS100xx sheet has no Mxxxx/LSL/USL columns (module-level functional test).</t>
-  </si>
-  <si>
-    <t>HOW TO UPDATE:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1. Set Include=FALSE for any parameter you want to hide from the report.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  2. Change the Mxxxx column to fix an incorrect measurement ID.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3. Edit LSL/USL if the auto-populated values need correction.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4. Add a Comment to explain why a parameter has no Mxxxx, is covered by</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     another measurement, or any other note you want in the report.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  5. You can add new rows — just fill in all columns and set Include=TRUE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  6. You can reorder rows by cut-pasting — the section grouping is driven</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     by the Section column, not by row position.</t>
-  </si>
-  <si>
-    <t>WHEN DONE EDITING:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Save this file, then run:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    python chapter7_config_manager.py report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  This will update Vision_Series_Test_Plan.md Chapter 7 and regenerate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  the Word document.</t>
-  </si>
-  <si>
-    <t>COLOR LEGEND:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Blue header columns  (DS_Min/Typ/Max) → values from the DATASHEET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Orange header columns (LSL/USL)        → values from CHECK_LIMITS tester DB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Grey rows                              → section headers (category grouping)</t>
-  </si>
-  <si>
-    <t>VDD3V3 supply voltage</t>
-  </si>
-  <si>
-    <t>VDD3V3</t>
-  </si>
-  <si>
-    <t>Operation temperature (junction)</t>
-  </si>
-  <si>
-    <t>-40</t>
-  </si>
-  <si>
-    <t>3.3V total supply current (average)</t>
-  </si>
-  <si>
-    <t>IVDD3V3_TOTAL_AVG</t>
-  </si>
-  <si>
-    <t>82.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum of analog + digital </t>
-  </si>
-  <si>
-    <t>3.3V digital supply current (average)</t>
-  </si>
-  <si>
-    <t>IVDD3V3_DIG_AVG</t>
-  </si>
-  <si>
-    <t>14.45</t>
-  </si>
-  <si>
-    <t>18.6</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>M0041</t>
-  </si>
-  <si>
-    <t>Channel combines DIG+PLL</t>
-  </si>
-  <si>
-    <t>3.3V analog supply current (average)</t>
-  </si>
-  <si>
-    <t>IVDD3V3_ANA_AVG</t>
-  </si>
-  <si>
-    <t>49.8</t>
-  </si>
-  <si>
-    <t>M0035</t>
-  </si>
-  <si>
-    <t>Active mode measurement</t>
-  </si>
-  <si>
-    <t>3.3V PLL supply current (average)</t>
-  </si>
-  <si>
-    <t>IVDD3V3_PLL_AVG</t>
-  </si>
-  <si>
-    <t>13.93</t>
-  </si>
-  <si>
-    <t>Included in DIG, no separate Power supply channel</t>
-  </si>
-  <si>
-    <t>Power consumption</t>
-  </si>
-  <si>
-    <t>Total power consumption</t>
-  </si>
-  <si>
-    <t>271.55</t>
-  </si>
-  <si>
-    <t>mW</t>
-  </si>
-  <si>
-    <t>Derived from IDD x VDD</t>
-  </si>
-  <si>
-    <t>Logic level inputs (GPIO)</t>
-  </si>
-  <si>
-    <t>VIL (GPIO input low threshold)</t>
-  </si>
-  <si>
-    <t>VIL</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>470</t>
-  </si>
-  <si>
-    <t>635</t>
-  </si>
-  <si>
-    <t>mV</t>
-  </si>
-  <si>
-    <t>VIH (GPIO input high threshold)</t>
-  </si>
-  <si>
-    <t>VIH</t>
-  </si>
-  <si>
-    <t>443</t>
-  </si>
-  <si>
-    <t>550</t>
-  </si>
-  <si>
-    <t>715</t>
-  </si>
-  <si>
-    <t>Hysteresis (GPIO)</t>
-  </si>
-  <si>
-    <t>Hysteresis</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>Logic level inputs (Video pins)</t>
-  </si>
-  <si>
-    <t>VIL (Video input low threshold)</t>
-  </si>
-  <si>
-    <t>1.147</t>
-  </si>
-  <si>
-    <t>1.328</t>
-  </si>
-  <si>
-    <t>1.689</t>
-  </si>
-  <si>
-    <t>VIH (Video input high threshold)</t>
-  </si>
-  <si>
-    <t>1.482</t>
-  </si>
-  <si>
-    <t>1.714</t>
-  </si>
-  <si>
-    <t>2.282</t>
-  </si>
-  <si>
-    <t>Hysteresis (Video)</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>387</t>
-  </si>
-  <si>
-    <t>593</t>
-  </si>
-  <si>
-    <t>M0021</t>
-  </si>
-  <si>
-    <t>Digital output levels (GPIO)</t>
-  </si>
-  <si>
-    <t>VOL (GPIO output low voltage)</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>M0029</t>
-  </si>
-  <si>
-    <t>VOH (GPIO output high voltage)</t>
-  </si>
-  <si>
-    <t>VDD-0.3</t>
-  </si>
-  <si>
-    <t>M0030</t>
-  </si>
-  <si>
-    <t>IOL (GPIO output low current)</t>
-  </si>
-  <si>
-    <t>IOL</t>
-  </si>
-  <si>
-    <t>M0031</t>
-  </si>
-  <si>
-    <t>T0006</t>
-  </si>
-  <si>
-    <t>IOH (GPIO output high current)</t>
-  </si>
-  <si>
-    <t>IOH</t>
-  </si>
-  <si>
-    <t>-20</t>
-  </si>
-  <si>
-    <t>M0032</t>
-  </si>
-  <si>
-    <t>Data rates</t>
-  </si>
-  <si>
-    <t>Parallel video data rate</t>
-  </si>
-  <si>
-    <t>DRin,par</t>
-  </si>
-  <si>
-    <t>M0156</t>
-  </si>
-  <si>
-    <t>T0023</t>
-  </si>
-  <si>
-    <t>Functional test</t>
-  </si>
-  <si>
-    <t>Downlink data rate (CXP)</t>
-  </si>
-  <si>
-    <t>DRdown</t>
-  </si>
-  <si>
-    <t>1.25</t>
-  </si>
-  <si>
-    <t>Gbps</t>
-  </si>
-  <si>
-    <t>T0022/T0023</t>
-  </si>
-  <si>
-    <t>Uplink data rate (CXP)</t>
-  </si>
-  <si>
-    <t>DRup</t>
-  </si>
-  <si>
-    <t>20.833</t>
-  </si>
-  <si>
-    <t>Mbps</t>
-  </si>
-  <si>
-    <t>T0020/T0021</t>
-  </si>
-  <si>
-    <t>Transceiver load impedance</t>
-  </si>
-  <si>
-    <t>ZL</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>Ω</t>
-  </si>
-  <si>
-    <t>Crystal oscillator</t>
-  </si>
-  <si>
-    <t>Crystal frequency</t>
-  </si>
-  <si>
-    <t>fXTAL</t>
-  </si>
-  <si>
-    <t>M0131</t>
-  </si>
-  <si>
-    <t>T0013</t>
-  </si>
-  <si>
-    <t>CAM LDO outputs</t>
-  </si>
-  <si>
-    <t>VDD1V8_CAM supply voltage</t>
-  </si>
-  <si>
-    <t>V_VDD1V8_CAM</t>
-  </si>
-  <si>
-    <t>1.7</t>
-  </si>
-  <si>
-    <t>1.9</t>
-  </si>
-  <si>
-    <t>M0214</t>
-  </si>
-  <si>
-    <t>T0012</t>
-  </si>
-  <si>
-    <t>VDD1V8_CAM load current</t>
-  </si>
-  <si>
-    <t>I_VDD1V8_CAM</t>
-  </si>
-  <si>
-    <t>VDD1V2_CAM reference voltage</t>
-  </si>
-  <si>
-    <t>V_VDD1V2_CAM</t>
-  </si>
-  <si>
-    <t>M0109</t>
-  </si>
-  <si>
-    <t>T0011</t>
-  </si>
-  <si>
-    <t>&gt; 1 MGy (100 Mrad)</t>
-  </si>
-  <si>
-    <t>&gt; 60</t>
-  </si>
-  <si>
-    <t>Input voltage (PVin, Vin)</t>
-  </si>
-  <si>
-    <t>PVin, Vin</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Output voltage (Vout)</t>
-  </si>
-  <si>
-    <t>Vout</t>
-  </si>
-  <si>
-    <t>0.9</t>
-  </si>
-  <si>
-    <t>Output current (active cooling)</t>
-  </si>
-  <si>
-    <t>Iout</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Switching frequency</t>
-  </si>
-  <si>
-    <t>fsw</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Input current (control, disabled)</t>
-  </si>
-  <si>
-    <t>Iin</t>
-  </si>
-  <si>
-    <t>Power short input</t>
-  </si>
-  <si>
-    <t>-10</t>
-  </si>
-  <si>
-    <t>M0001</t>
-  </si>
-  <si>
-    <t>T0001</t>
-  </si>
-  <si>
-    <t>Power short output</t>
-  </si>
-  <si>
-    <t>M0002</t>
-  </si>
-  <si>
-    <t>T0002</t>
-  </si>
-  <si>
-    <t>Enable</t>
-  </si>
-  <si>
-    <t>Enable start threshold (VIH)</t>
-  </si>
-  <si>
-    <t>EnStartTh</t>
-  </si>
-  <si>
-    <t>0.77</t>
-  </si>
-  <si>
-    <t>0.815</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>M0007</t>
-  </si>
-  <si>
-    <t>Enable stop threshold (VIL)</t>
-  </si>
-  <si>
-    <t>EnStopTh</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>M0008</t>
-  </si>
-  <si>
-    <t>Enable hysteresis</t>
-  </si>
-  <si>
-    <t>Hyst</t>
-  </si>
-  <si>
     <t>Inv_Enable functionality</t>
   </si>
   <si>
@@ -1625,9 +1688,6 @@
     <t>kΩ</t>
   </si>
   <si>
-    <t>Guaranteed by design</t>
-  </si>
-  <si>
     <t>Protections</t>
   </si>
   <si>
@@ -1811,64 +1871,7 @@
     <t>2x MAG-PSU00001-NP</t>
   </si>
   <si>
-    <t>This is a design target, related to test parameter: saturation limit. This is tested only during characterization</t>
-  </si>
-  <si>
-    <t>DN/p</t>
-  </si>
-  <si>
-    <t>mV/e-</t>
-  </si>
-  <si>
-    <t>M3812</t>
-  </si>
-  <si>
-    <t>M3807</t>
-  </si>
-  <si>
-    <t>M3806</t>
-  </si>
-  <si>
-    <t>e-/s/px</t>
-  </si>
-  <si>
-    <t>M3813</t>
-  </si>
-  <si>
-    <t>M3815</t>
-  </si>
-  <si>
-    <t>M3808</t>
-  </si>
-  <si>
-    <t>M3809</t>
-  </si>
-  <si>
-    <t>% of mean</t>
-  </si>
-  <si>
-    <t>Fixed to 10b for all tests</t>
-  </si>
-  <si>
-    <t>M3802</t>
-  </si>
-  <si>
-    <t>M3800</t>
-  </si>
-  <si>
-    <t>T0038</t>
-  </si>
-  <si>
-    <t>T0024</t>
-  </si>
-  <si>
-    <t>M0130</t>
-  </si>
-  <si>
-    <t>Only tested at speed during characterization (FHD30 mode), production testing uses FHD10, HD40 and VGA50 mode what is at half of the max speed</t>
-  </si>
-  <si>
-    <t>Features are tested during characterization: Exposure time, sub-sampling, X-Y mirroring, ADC resolution</t>
+    <t>Typical pre-irrad value (0 Gy TID, RT)</t>
   </si>
 </sst>
 </file>
@@ -1978,7 +1981,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -2053,11 +2056,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2092,6 +2110,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2402,7 +2426,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -2410,12 +2434,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -2423,62 +2447,62 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -2486,7 +2510,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
@@ -2494,47 +2518,47 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -2542,27 +2566,27 @@
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -2570,22 +2594,22 @@
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -2677,10 +2701,10 @@
         <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>89</v>
@@ -2708,13 +2732,13 @@
         <v>13</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9" t="s">
@@ -2756,14 +2780,14 @@
         <v>45</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="9" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9" t="s">
@@ -2776,7 +2800,7 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2787,25 +2811,25 @@
         <v>45</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>50</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>52</v>
@@ -2817,7 +2841,7 @@
         <v>0.1</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -2828,21 +2852,21 @@
         <v>45</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9" t="s">
         <v>50</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>52</v>
@@ -2854,7 +2878,7 @@
         <v>0.06</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -2865,14 +2889,14 @@
         <v>45</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9" t="s">
@@ -2885,7 +2909,7 @@
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
       <c r="M9" s="9" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -2893,7 +2917,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -2912,19 +2936,19 @@
         <v>44</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9" t="s">
@@ -2933,7 +2957,7 @@
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -2941,7 +2965,7 @@
         <v>44</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -2960,25 +2984,25 @@
         <v>44</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>99</v>
@@ -2999,25 +3023,25 @@
         <v>44</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>95</v>
@@ -3038,25 +3062,25 @@
         <v>44</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>103</v>
@@ -3077,7 +3101,7 @@
         <v>44</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -3096,22 +3120,22 @@
         <v>44</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>19</v>
@@ -3135,22 +3159,22 @@
         <v>44</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>19</v>
@@ -3174,28 +3198,28 @@
         <v>44</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>245</v>
-      </c>
       <c r="I19" s="9" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>67</v>
@@ -3213,7 +3237,7 @@
         <v>44</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -3232,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>109</v>
@@ -3243,13 +3267,13 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>91</v>
@@ -3265,16 +3289,16 @@
         <v>0</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>107</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
@@ -3282,7 +3306,7 @@
         <v>19</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>91</v>
@@ -3298,13 +3322,13 @@
         <v>0</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>33</v>
@@ -3315,10 +3339,10 @@
         <v>50</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="K23" s="9">
         <v>0.02</v>
@@ -3331,16 +3355,16 @@
         <v>0</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
@@ -3348,10 +3372,10 @@
         <v>50</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="9">
@@ -3364,7 +3388,7 @@
         <v>44</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -3383,13 +3407,13 @@
         <v>44</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -3400,15 +3424,15 @@
         <v>35</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
       <c r="M26" s="9" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -3416,25 +3440,25 @@
         <v>0</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="G27" s="9"/>
       <c r="H27" s="9" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
@@ -3445,25 +3469,25 @@
         <v>0</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G28" s="9"/>
       <c r="H28" s="9" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="9" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
@@ -3474,21 +3498,21 @@
         <v>0</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="G29" s="9"/>
       <c r="H29" s="9" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
@@ -3501,7 +3525,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -3520,13 +3544,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>32</v>
@@ -3541,10 +3565,10 @@
         <v>35</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="K31" s="9">
         <v>19500000</v>
@@ -3559,7 +3583,7 @@
         <v>44</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -3578,31 +3602,31 @@
         <v>44</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="K33" s="9">
         <v>1.7</v>
@@ -3617,13 +3641,13 @@
         <v>0</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
@@ -3634,10 +3658,10 @@
         <v>50</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
@@ -3648,31 +3672,31 @@
         <v>44</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>79</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="K35" s="9">
         <v>1.18</v>
@@ -3687,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -3706,23 +3730,23 @@
         <v>0</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K37" s="9"/>
       <c r="L37" s="9"/>
@@ -3733,23 +3757,23 @@
         <v>0</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K38" s="9"/>
       <c r="L38" s="9"/>
@@ -3768,7 +3792,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4640,15 +4664,15 @@
         <v>35</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>610</v>
+        <v>116</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>609</v>
+        <v>117</v>
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9" t="s">
-        <v>611</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -4659,10 +4683,10 @@
         <v>105</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
@@ -4673,15 +4697,15 @@
         <v>35</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>610</v>
+        <v>116</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>609</v>
+        <v>117</v>
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
       <c r="M29" s="9" t="s">
-        <v>611</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -4689,7 +4713,7 @@
         <v>44</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4708,31 +4732,31 @@
         <v>44</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
@@ -4743,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4762,23 +4786,23 @@
         <v>0</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
@@ -4789,23 +4813,23 @@
         <v>0</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
@@ -4816,7 +4840,7 @@
         <v>44</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C35" s="21"/>
       <c r="D35" s="21"/>
@@ -4835,15 +4859,15 @@
         <v>44</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
       <c r="F36" s="22" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G36" s="22"/>
       <c r="H36" s="22"/>
@@ -4852,7 +4876,7 @@
       <c r="K36" s="23"/>
       <c r="L36" s="23"/>
       <c r="M36" s="16" t="s">
-        <v>531</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -4860,15 +4884,15 @@
         <v>44</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D37" s="22"/>
       <c r="E37" s="22"/>
       <c r="F37" s="22" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G37" s="22"/>
       <c r="H37" s="22"/>
@@ -4877,7 +4901,7 @@
       <c r="K37" s="23"/>
       <c r="L37" s="23"/>
       <c r="M37" s="16" t="s">
-        <v>531</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -4885,15 +4909,15 @@
         <v>44</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D38" s="22"/>
       <c r="E38" s="22"/>
       <c r="F38" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G38" s="22"/>
       <c r="H38" s="22"/>
@@ -4902,7 +4926,7 @@
       <c r="K38" s="23"/>
       <c r="L38" s="23"/>
       <c r="M38" s="16" t="s">
-        <v>531</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
@@ -4910,15 +4934,15 @@
         <v>44</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D39" s="22"/>
       <c r="E39" s="22"/>
       <c r="F39" s="22" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G39" s="22"/>
       <c r="H39" s="22"/>
@@ -4927,7 +4951,7 @@
       <c r="K39" s="23"/>
       <c r="L39" s="23"/>
       <c r="M39" s="16" t="s">
-        <v>531</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
@@ -4935,26 +4959,30 @@
         <v>44</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D40" s="22"/>
       <c r="E40" s="22"/>
-      <c r="F40" s="22" t="s">
-        <v>145</v>
+      <c r="F40" s="22">
+        <v>107000</v>
       </c>
       <c r="G40" s="22"/>
       <c r="H40" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="I40" s="22"/>
-      <c r="J40" s="22"/>
+        <v>149</v>
+      </c>
+      <c r="I40" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="J40" s="22" t="s">
+        <v>151</v>
+      </c>
       <c r="K40" s="23"/>
       <c r="L40" s="23"/>
       <c r="M40" s="16" t="s">
-        <v>593</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -4962,83 +4990,85 @@
         <v>44</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D41" s="22"/>
       <c r="E41" s="22"/>
-      <c r="F41" s="22" t="s">
-        <v>148</v>
+      <c r="F41" s="22">
+        <v>1.2E-2</v>
       </c>
       <c r="G41" s="22"/>
       <c r="H41" s="24" t="s">
-        <v>595</v>
+        <v>154</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>606</v>
+        <v>155</v>
       </c>
       <c r="J41" s="24" t="s">
-        <v>608</v>
+        <v>151</v>
       </c>
       <c r="K41" s="23"/>
       <c r="L41" s="23"/>
       <c r="M41" s="16"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="G42" s="22"/>
-      <c r="H42" s="24" t="s">
-        <v>594</v>
-      </c>
-      <c r="I42" s="24" t="s">
-        <v>607</v>
-      </c>
-      <c r="J42" s="24" t="s">
-        <v>608</v>
-      </c>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="16"/>
+      <c r="A42" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="I42" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="J42" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="K42" s="27"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="26" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="22" t="s">
         <v>44</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D43" s="22"/>
       <c r="E43" s="22"/>
-      <c r="F43" s="22" t="s">
-        <v>152</v>
+      <c r="F43" s="22">
+        <v>76</v>
       </c>
       <c r="G43" s="22"/>
       <c r="H43" s="22" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>596</v>
+        <v>161</v>
       </c>
       <c r="J43" s="24" t="s">
-        <v>608</v>
+        <v>151</v>
       </c>
       <c r="K43" s="23"/>
       <c r="L43" s="23"/>
@@ -5049,25 +5079,25 @@
         <v>44</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D44" s="22"/>
       <c r="E44" s="22"/>
       <c r="F44" s="22" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="G44" s="22"/>
       <c r="H44" s="22" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="I44" s="24" t="s">
-        <v>597</v>
+        <v>165</v>
       </c>
       <c r="J44" s="24" t="s">
-        <v>608</v>
+        <v>151</v>
       </c>
       <c r="K44" s="23"/>
       <c r="L44" s="23"/>
@@ -5078,25 +5108,25 @@
         <v>44</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="D45" s="22"/>
       <c r="E45" s="22"/>
-      <c r="F45" s="22" t="s">
-        <v>157</v>
+      <c r="F45" s="22">
+        <v>50.3</v>
       </c>
       <c r="G45" s="22"/>
       <c r="H45" s="22" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="I45" s="24" t="s">
-        <v>598</v>
+        <v>167</v>
       </c>
       <c r="J45" s="24" t="s">
-        <v>608</v>
+        <v>151</v>
       </c>
       <c r="K45" s="23"/>
       <c r="L45" s="23"/>
@@ -5107,142 +5137,154 @@
         <v>44</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D46" s="22"/>
       <c r="E46" s="22"/>
-      <c r="F46" s="22" t="s">
-        <v>159</v>
+      <c r="F46" s="22">
+        <v>536</v>
       </c>
       <c r="G46" s="22"/>
       <c r="H46" s="25" t="s">
-        <v>599</v>
+        <v>169</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>600</v>
+        <v>170</v>
       </c>
       <c r="J46" s="24" t="s">
-        <v>608</v>
+        <v>151</v>
       </c>
       <c r="K46" s="23"/>
       <c r="L46" s="23"/>
-      <c r="M46" s="22"/>
+      <c r="M46" s="24" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="22" t="s">
         <v>44</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D47" s="22"/>
       <c r="E47" s="22"/>
-      <c r="F47" s="22" t="s">
-        <v>161</v>
+      <c r="F47" s="22">
+        <v>1596</v>
       </c>
       <c r="G47" s="22"/>
       <c r="H47" s="25" t="s">
-        <v>599</v>
+        <v>169</v>
       </c>
       <c r="I47" s="24" t="s">
-        <v>601</v>
+        <v>172</v>
       </c>
       <c r="J47" s="24" t="s">
-        <v>608</v>
+        <v>151</v>
       </c>
       <c r="K47" s="23"/>
       <c r="L47" s="23"/>
-      <c r="M47" s="22"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M47" s="24" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22" t="s">
         <v>44</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D48" s="22"/>
       <c r="E48" s="22"/>
-      <c r="F48" s="22" t="s">
-        <v>163</v>
+      <c r="F48" s="22">
+        <v>159</v>
       </c>
       <c r="G48" s="22"/>
       <c r="H48" s="22" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I48" s="24" t="s">
-        <v>602</v>
+        <v>174</v>
       </c>
       <c r="J48" s="24" t="s">
-        <v>608</v>
+        <v>151</v>
       </c>
       <c r="K48" s="23"/>
       <c r="L48" s="23"/>
-      <c r="M48" s="22"/>
-    </row>
-    <row r="49" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="M48" s="22" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="22" t="s">
         <v>44</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="D49" s="22"/>
       <c r="E49" s="22"/>
-      <c r="F49" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="G49" s="22">
-        <v>2.5</v>
-      </c>
+      <c r="F49" s="22">
+        <v>1.21</v>
+      </c>
+      <c r="G49" s="22"/>
       <c r="H49" s="25" t="s">
-        <v>604</v>
+        <v>177</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>603</v>
+        <v>178</v>
       </c>
       <c r="J49" s="24" t="s">
-        <v>608</v>
+        <v>151</v>
       </c>
       <c r="K49" s="23"/>
       <c r="L49" s="23"/>
-      <c r="M49" s="22"/>
+      <c r="M49" s="22" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-      <c r="I50" s="22"/>
-      <c r="J50" s="22"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="23"/>
-      <c r="M50" s="16" t="s">
-        <v>531</v>
+      <c r="A50" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C50" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26">
+        <v>5.62</v>
+      </c>
+      <c r="G50" s="26"/>
+      <c r="H50" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="I50" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="J50" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="K50" s="27"/>
+      <c r="L50" s="27"/>
+      <c r="M50" s="29" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
@@ -5250,15 +5292,15 @@
         <v>44</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D51" s="22"/>
       <c r="E51" s="22"/>
       <c r="F51" s="22" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G51" s="22"/>
       <c r="H51" s="22"/>
@@ -5266,8 +5308,8 @@
       <c r="J51" s="22"/>
       <c r="K51" s="23"/>
       <c r="L51" s="23"/>
-      <c r="M51" s="24" t="s">
-        <v>612</v>
+      <c r="M51" s="16" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -5275,15 +5317,15 @@
         <v>44</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="D52" s="22"/>
       <c r="E52" s="22"/>
       <c r="F52" s="22" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="G52" s="22"/>
       <c r="H52" s="22"/>
@@ -5291,8 +5333,8 @@
       <c r="J52" s="22"/>
       <c r="K52" s="23"/>
       <c r="L52" s="23"/>
-      <c r="M52" s="16" t="s">
-        <v>531</v>
+      <c r="M52" s="24" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
@@ -5300,15 +5342,15 @@
         <v>44</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="D53" s="22"/>
       <c r="E53" s="22"/>
       <c r="F53" s="22" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="G53" s="22"/>
       <c r="H53" s="22"/>
@@ -5316,8 +5358,8 @@
       <c r="J53" s="22"/>
       <c r="K53" s="23"/>
       <c r="L53" s="23"/>
-      <c r="M53" s="24" t="s">
-        <v>605</v>
+      <c r="M53" s="16" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
@@ -5325,24 +5367,49 @@
         <v>44</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>175</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="D54" s="22"/>
       <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
+      <c r="F54" s="22" t="s">
+        <v>192</v>
+      </c>
       <c r="G54" s="22"/>
       <c r="H54" s="22"/>
       <c r="I54" s="22"/>
       <c r="J54" s="22"/>
       <c r="K54" s="23"/>
       <c r="L54" s="23"/>
-      <c r="M54" s="16" t="s">
-        <v>531</v>
+      <c r="M54" s="24" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
+      <c r="K55" s="23"/>
+      <c r="L55" s="23"/>
+      <c r="M55" s="16" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -5440,17 +5507,17 @@
         <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>19</v>
@@ -5469,17 +5536,17 @@
         <v>13</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>19</v>
@@ -5498,20 +5565,20 @@
         <v>13</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>40</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -5527,17 +5594,17 @@
         <v>13</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>35</v>
@@ -5553,7 +5620,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -5572,17 +5639,17 @@
         <v>0</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9" t="s">
@@ -5599,14 +5666,14 @@
         <v>0</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9" t="s">
@@ -5616,10 +5683,10 @@
         <v>50</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="K9" s="9">
         <v>-0.01</v>
@@ -5634,14 +5701,14 @@
         <v>0</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9" t="s">
@@ -5651,10 +5718,10 @@
         <v>50</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="K10" s="9">
         <v>-0.01</v>
@@ -5669,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -5688,31 +5755,31 @@
         <v>0</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="K12" s="9">
         <v>0.77</v>
@@ -5727,31 +5794,31 @@
         <v>0</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="K13" s="9">
         <v>0.67</v>
@@ -5766,16 +5833,16 @@
         <v>0</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>159</v>
+        <v>385</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
@@ -5783,10 +5850,10 @@
         <v>19</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="K14" s="9">
         <v>0.05</v>
@@ -5799,30 +5866,30 @@
         <v>0</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="K15" s="9">
         <v>1</v>
       </c>
       <c r="L15" s="9"/>
       <c r="M15" s="9" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -5830,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -5849,24 +5916,24 @@
         <v>0</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>91</v>
@@ -5882,21 +5949,21 @@
         <v>0</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>74</v>
@@ -5915,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -5934,25 +6001,25 @@
         <v>0</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>115</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>83</v>
@@ -5973,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>34</v>
@@ -5989,10 +6056,10 @@
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="9" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>52</v>
@@ -6008,13 +6075,13 @@
         <v>0</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>34</v>
@@ -6024,10 +6091,10 @@
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>52</v>
@@ -6043,7 +6110,7 @@
         <v>0</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -6062,27 +6129,27 @@
         <v>0</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="K24" s="9">
         <v>-10</v>
@@ -6095,29 +6162,29 @@
         <v>0</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>89</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="K25" s="9">
         <v>2.97</v>
@@ -6132,31 +6199,31 @@
         <v>0</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K26" s="9">
         <v>0.56999999999999995</v>
@@ -6171,7 +6238,7 @@
         <v>0</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -6190,31 +6257,31 @@
         <v>0</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="K28" s="9">
         <v>4.4000000000000004</v>
@@ -6229,31 +6296,31 @@
         <v>0</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="K29" s="9">
         <v>4.12</v>
@@ -6268,16 +6335,16 @@
         <v>0</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
@@ -6285,10 +6352,10 @@
         <v>19</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="K30" s="9">
         <v>0.1</v>
@@ -6301,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -6320,22 +6387,22 @@
         <v>0</v>
       </c>
       <c r="B32" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="G32" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>401</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>19</v>
@@ -6344,7 +6411,7 @@
         <v>99</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K32" s="9">
         <v>0.52</v>
@@ -6359,22 +6426,22 @@
         <v>0</v>
       </c>
       <c r="B33" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>401</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>19</v>
@@ -6383,7 +6450,7 @@
         <v>95</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K33" s="9">
         <v>0.52</v>
@@ -6398,22 +6465,22 @@
         <v>0</v>
       </c>
       <c r="B34" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>401</v>
-      </c>
       <c r="F34" s="9" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>19</v>
@@ -6422,7 +6489,7 @@
         <v>103</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K34" s="9">
         <v>0.6</v>
@@ -6437,22 +6504,22 @@
         <v>0</v>
       </c>
       <c r="B35" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>401</v>
-      </c>
       <c r="F35" s="9" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>19</v>
@@ -6461,7 +6528,7 @@
         <v>111</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K35" s="9">
         <v>0.6</v>
@@ -6476,31 +6543,31 @@
         <v>0</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K36" s="9">
         <v>-10.5</v>
@@ -6515,31 +6582,31 @@
         <v>0</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>29</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K37" s="9">
         <v>2.5</v>
@@ -6554,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -6573,29 +6640,29 @@
         <v>0</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="9" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="K39" s="9">
         <v>0.2</v>
@@ -6610,7 +6677,7 @@
         <v>0</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -6629,16 +6696,16 @@
         <v>0</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="9"/>
@@ -6646,10 +6713,10 @@
         <v>19</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="K41" s="9">
         <v>0.9</v>
@@ -6662,27 +6729,27 @@
         <v>0</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="9" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="K42" s="9"/>
       <c r="L42" s="9">
@@ -6695,7 +6762,7 @@
         <v>0</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -6714,27 +6781,27 @@
         <v>0</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="H44" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="K44" s="9"/>
       <c r="L44" s="9">
@@ -6747,7 +6814,7 @@
         <v>0</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
@@ -6766,29 +6833,29 @@
         <v>0</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>40</v>
       </c>
       <c r="F46" s="9"/>
       <c r="G46" s="9" t="s">
-        <v>470</v>
+        <v>491</v>
       </c>
       <c r="H46" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="K46" s="9">
         <v>0</v>
@@ -6803,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
@@ -6822,29 +6889,29 @@
         <v>0</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="F48" s="9"/>
       <c r="G48" s="9" t="s">
         <v>115</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="K48" s="9">
         <v>35</v>
@@ -6859,7 +6926,7 @@
         <v>0</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
@@ -6878,23 +6945,23 @@
         <v>0</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D50" s="9"/>
       <c r="E50" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F50" s="9"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K50" s="9"/>
       <c r="L50" s="9"/>
@@ -6905,23 +6972,23 @@
         <v>0</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F51" s="9"/>
       <c r="G51" s="9"/>
       <c r="H51" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="9" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="K51" s="9"/>
       <c r="L51" s="9"/>
@@ -6935,13 +7002,13 @@
         <v>13</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="F52" s="11"/>
       <c r="G52" s="11" t="s">
@@ -6962,10 +7029,10 @@
         <v>13</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>40</v>
@@ -6975,7 +7042,7 @@
         <v>32</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="I53" s="11"/>
       <c r="J53" s="11"/>
@@ -6991,17 +7058,17 @@
         <v>13</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="F54" s="11"/>
       <c r="G54" s="11" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="H54" s="11" t="s">
         <v>43</v>
@@ -7020,17 +7087,17 @@
         <v>13</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="F55" s="11"/>
       <c r="G55" s="11" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="H55" s="11" t="s">
         <v>50</v>
@@ -7049,20 +7116,20 @@
         <v>13</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="F56" s="11"/>
       <c r="G56" s="11" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="I56" s="11"/>
       <c r="J56" s="11"/>
@@ -7078,10 +7145,10 @@
         <v>13</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
@@ -7105,10 +7172,10 @@
         <v>13</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="11"/>
@@ -7129,20 +7196,20 @@
         <v>44</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="F59" s="11"/>
       <c r="G59" s="11" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="H59" s="11" t="s">
         <v>19</v>
@@ -7152,7 +7219,7 @@
       <c r="K59" s="12"/>
       <c r="L59" s="12"/>
       <c r="M59" s="16" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -7160,28 +7227,28 @@
         <v>44</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="E60" s="11"/>
       <c r="F60" s="11"/>
       <c r="G60" s="11" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="I60" s="11"/>
       <c r="J60" s="11"/>
       <c r="K60" s="12"/>
       <c r="L60" s="12"/>
       <c r="M60" s="16" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -7189,28 +7256,28 @@
         <v>44</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="11"/>
       <c r="G61" s="11" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="I61" s="11"/>
       <c r="J61" s="11"/>
       <c r="K61" s="12"/>
       <c r="L61" s="12"/>
       <c r="M61" s="16" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -7218,7 +7285,7 @@
         <v>44</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="15"/>
@@ -7237,13 +7304,13 @@
         <v>44</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="11" t="s">
@@ -7251,14 +7318,14 @@
       </c>
       <c r="G63" s="11"/>
       <c r="H63" s="11" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="I63" s="11"/>
       <c r="J63" s="11"/>
       <c r="K63" s="12"/>
       <c r="L63" s="12"/>
       <c r="M63" s="16" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -7266,13 +7333,13 @@
         <v>44</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="E64" s="11"/>
       <c r="F64" s="11" t="s">
@@ -7280,14 +7347,14 @@
       </c>
       <c r="G64" s="11"/>
       <c r="H64" s="11" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="I64" s="11"/>
       <c r="J64" s="11"/>
       <c r="K64" s="12"/>
       <c r="L64" s="12"/>
       <c r="M64" s="16" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -7295,7 +7362,7 @@
         <v>44</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="C65" s="15"/>
       <c r="D65" s="15"/>
@@ -7314,28 +7381,28 @@
         <v>44</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="E66" s="11"/>
       <c r="F66" s="11" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="G66" s="11"/>
       <c r="H66" s="11" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="I66" s="11"/>
       <c r="J66" s="11"/>
       <c r="K66" s="12"/>
       <c r="L66" s="12"/>
       <c r="M66" s="16" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -7343,13 +7410,13 @@
         <v>44</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="E67" s="11"/>
       <c r="F67" s="11" t="s">
@@ -7364,7 +7431,7 @@
       <c r="K67" s="12"/>
       <c r="L67" s="12"/>
       <c r="M67" s="16" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -7372,13 +7439,13 @@
         <v>44</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="E68" s="11"/>
       <c r="F68" s="11" t="s">
@@ -7386,14 +7453,14 @@
       </c>
       <c r="G68" s="11"/>
       <c r="H68" s="11" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="I68" s="11"/>
       <c r="J68" s="11"/>
       <c r="K68" s="12"/>
       <c r="L68" s="12"/>
       <c r="M68" s="16" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
@@ -7401,7 +7468,7 @@
         <v>44</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15"/>
@@ -7420,13 +7487,13 @@
         <v>44</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="E70" s="11"/>
       <c r="F70" s="11">
@@ -7437,10 +7504,10 @@
         <v>19</v>
       </c>
       <c r="I70" s="16" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="J70" s="16" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="K70" s="12"/>
       <c r="L70" s="12"/>
@@ -7451,13 +7518,13 @@
         <v>44</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="E71" s="11"/>
       <c r="F71" s="11">
@@ -7468,10 +7535,10 @@
         <v>19</v>
       </c>
       <c r="I71" s="16" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="J71" s="16" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="K71" s="12"/>
       <c r="L71" s="12"/>
@@ -7482,7 +7549,7 @@
         <v>44</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C72" s="15"/>
       <c r="D72" s="15"/>
@@ -7501,27 +7568,27 @@
         <v>44</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="E73" s="11"/>
       <c r="F73" s="11" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="G73" s="11"/>
       <c r="H73" s="11" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="K73" s="11">
         <v>0.77</v>
@@ -7536,27 +7603,27 @@
         <v>44</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="11" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="G74" s="11"/>
       <c r="H74" s="11" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="K74" s="11">
         <v>0.67</v>
@@ -7571,13 +7638,13 @@
         <v>44</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="E75" s="11"/>
       <c r="F75" s="11" t="s">
@@ -7585,14 +7652,14 @@
       </c>
       <c r="G75" s="11"/>
       <c r="H75" s="11" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="I75" s="11"/>
       <c r="J75" s="11"/>
       <c r="K75" s="12"/>
       <c r="L75" s="12"/>
       <c r="M75" s="16" t="s">
-        <v>531</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -7600,7 +7667,7 @@
         <v>44</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="C76" s="15"/>
       <c r="D76" s="15"/>
@@ -7619,28 +7686,28 @@
         <v>44</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="E77" s="11"/>
       <c r="F77" s="11" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="G77" s="11"/>
       <c r="H77" s="11" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="I77" s="11"/>
       <c r="J77" s="11"/>
       <c r="K77" s="12"/>
       <c r="L77" s="12"/>
       <c r="M77" s="16" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -7648,28 +7715,28 @@
         <v>44</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>537</v>
+        <v>557</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="E78" s="11"/>
       <c r="F78" s="11" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="G78" s="11"/>
       <c r="H78" s="11" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="I78" s="11"/>
       <c r="J78" s="11"/>
       <c r="K78" s="12"/>
       <c r="L78" s="12"/>
       <c r="M78" s="16" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -7677,17 +7744,17 @@
         <v>44</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="E79" s="11"/>
       <c r="F79" s="11" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="G79" s="11"/>
       <c r="H79" s="11" t="s">
@@ -7698,7 +7765,7 @@
       <c r="K79" s="12"/>
       <c r="L79" s="12"/>
       <c r="M79" s="16" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
@@ -7706,17 +7773,17 @@
         <v>44</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="E80" s="11"/>
       <c r="F80" s="11" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="G80" s="11"/>
       <c r="H80" s="11" t="s">
@@ -7727,7 +7794,7 @@
       <c r="K80" s="12"/>
       <c r="L80" s="12"/>
       <c r="M80" s="16" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -7735,7 +7802,7 @@
         <v>44</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15"/>
@@ -7754,27 +7821,27 @@
         <v>44</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="11"/>
       <c r="G82" s="11" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="I82" s="16" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="J82" s="16" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="K82" s="12"/>
       <c r="L82" s="12"/>
@@ -7785,7 +7852,7 @@
         <v>44</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15"/>
@@ -7804,27 +7871,27 @@
         <v>44</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="11" t="s">
-        <v>554</v>
+        <v>574</v>
       </c>
       <c r="G84" s="11"/>
       <c r="H84" s="11" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K84" s="11">
         <v>2.5</v>
@@ -7839,27 +7906,27 @@
         <v>44</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="E85" s="11"/>
       <c r="F85" s="11" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="G85" s="11"/>
       <c r="H85" s="11" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K85" s="11">
         <v>-10.5</v>
@@ -7874,7 +7941,7 @@
         <v>44</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="C86" s="15"/>
       <c r="D86" s="15"/>
@@ -7893,28 +7960,28 @@
         <v>44</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="E87" s="11"/>
       <c r="F87" s="11" t="s">
-        <v>558</v>
+        <v>578</v>
       </c>
       <c r="G87" s="11"/>
       <c r="H87" s="11" t="s">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="I87" s="11"/>
       <c r="J87" s="11"/>
       <c r="K87" s="12"/>
       <c r="L87" s="12"/>
       <c r="M87" s="16" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -7922,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="C88" s="15"/>
       <c r="D88" s="15"/>
@@ -7941,25 +8008,25 @@
         <v>0</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>561</v>
+        <v>581</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>562</v>
+        <v>582</v>
       </c>
       <c r="E89" s="11"/>
       <c r="F89" s="11"/>
       <c r="G89" s="11" t="s">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="H89" s="11" t="s">
         <v>19</v>
       </c>
       <c r="I89" s="11"/>
       <c r="J89" s="11" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="K89" s="12"/>
       <c r="L89" s="12"/>
@@ -8047,25 +8114,25 @@
         <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="J3" s="9"/>
     </row>
@@ -8077,10 +8144,10 @@
         <v>13</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>569</v>
+        <v>589</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>40</v>
@@ -8103,18 +8170,18 @@
         <v>13</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -8127,16 +8194,16 @@
         <v>13</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9" t="s">
-        <v>574</v>
+        <v>594</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -8149,16 +8216,16 @@
         <v>13</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -8171,20 +8238,20 @@
         <v>13</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>40</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
@@ -8194,7 +8261,7 @@
         <v>44</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -8210,26 +8277,26 @@
         <v>44</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>50</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="J10" s="9"/>
     </row>
@@ -8238,21 +8305,21 @@
         <v>44</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
@@ -8262,7 +8329,7 @@
         <v>0</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -8278,13 +8345,13 @@
         <v>0</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
@@ -8298,13 +8365,13 @@
         <v>0</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
@@ -8318,13 +8385,13 @@
         <v>0</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
@@ -8338,7 +8405,7 @@
         <v>0</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -8354,22 +8421,22 @@
         <v>0</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J17" s="9"/>
     </row>
@@ -8378,20 +8445,20 @@
         <v>0</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J18" s="9"/>
     </row>
